--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487669_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487669_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4471</v>
+        <v>12.2527</v>
       </c>
       <c r="E2" t="n">
-        <v>8.606400000000001</v>
+        <v>8.4832</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8406</v>
+        <v>3.7696</v>
       </c>
       <c r="G2" t="n">
-        <v>6.76</v>
+        <v>10.2971</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3894</v>
+        <v>7.2863</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3706</v>
+        <v>3.0108</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0269</v>
+        <v>8.4572</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3069</v>
+        <v>6.5086</v>
       </c>
       <c r="L2" t="n">
-        <v>2.72</v>
+        <v>1.9486</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7332</v>
+        <v>1.8399</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0825</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6506</v>
+        <v>1.0622</v>
       </c>
       <c r="P2" t="n">
         <v>0.5821</v>
@@ -610,19 +610,19 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9289</v>
+        <v>1.7034</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3736</v>
+        <v>1.326</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4448</v>
+        <v>0.3774</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1761</v>
+        <v>-0.3299</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1761</v>
+        <v>-0.3299</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.8697</v>
+        <v>10.5368</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1819</v>
+        <v>7.5054</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6878</v>
+        <v>3.0314</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2971</v>
+        <v>6.76</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2863</v>
+        <v>3.3894</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0108</v>
+        <v>3.3706</v>
       </c>
       <c r="J3" t="n">
-        <v>8.4572</v>
+        <v>5.0269</v>
       </c>
       <c r="K3" t="n">
-        <v>6.5086</v>
+        <v>2.3069</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9486</v>
+        <v>2.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8399</v>
+        <v>1.7332</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.0825</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0622</v>
+        <v>0.6506</v>
       </c>
       <c r="P3" t="n">
         <v>0.5821</v>
@@ -688,19 +688,19 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3203</v>
+        <v>2.0186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0247</v>
+        <v>2.2726</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2957</v>
+        <v>-0.254</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3299</v>
+        <v>1.1761</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3299</v>
+        <v>1.1761</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.889</v>
+        <v>7.8473</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9891</v>
+        <v>6.2705</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8999</v>
+        <v>1.5768</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6312</v>
+        <v>6.3503</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1565</v>
+        <v>1.4665</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4746</v>
+        <v>4.8838</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0817</v>
+        <v>5.8295</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8156</v>
+        <v>0.6509</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8973</v>
+        <v>5.1786</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5495</v>
+        <v>0.5208</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9721</v>
+        <v>0.8156</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4227</v>
+        <v>-0.2948</v>
       </c>
       <c r="P4" t="n">
         <v>0.3881</v>
@@ -766,19 +766,19 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3638</v>
+        <v>1.109</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3717</v>
+        <v>1.4112</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9922</v>
+        <v>-0.3022</v>
       </c>
       <c r="V4" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.2462</v>
+        <v>7.3618</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9692</v>
+        <v>4.7889</v>
       </c>
       <c r="F5" t="n">
-        <v>1.277</v>
+        <v>2.5728</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3503</v>
+        <v>3.6312</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4665</v>
+        <v>0.1565</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8838</v>
+        <v>3.4746</v>
       </c>
       <c r="J5" t="n">
-        <v>5.8295</v>
+        <v>3.0817</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6509</v>
+        <v>-0.8156</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1786</v>
+        <v>3.8973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5208</v>
+        <v>0.5495</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8156</v>
+        <v>0.9721</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2948</v>
+        <v>-0.4227</v>
       </c>
       <c r="P5" t="n">
         <v>0.3881</v>
@@ -844,19 +844,19 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4921</v>
+        <v>1.8366</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1099</v>
+        <v>1.1715</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.602</v>
+        <v>0.6651</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6199</v>
+        <v>3.082</v>
       </c>
       <c r="E6" t="n">
-        <v>0.483</v>
+        <v>3.2192</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1368</v>
+        <v>-0.1372</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0972</v>
+        <v>2.3238</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3131</v>
+        <v>2.2376</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4103</v>
+        <v>0.0862</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6475</v>
+        <v>2.7377</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5406</v>
+        <v>2.1009</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8931</v>
+        <v>0.6368</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7447</v>
+        <v>-0.4138</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2275</v>
+        <v>0.1367</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5172</v>
+        <v>-0.5506</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5523</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>4.0749</v>
+        <v>-0.5254</v>
       </c>
       <c r="T6" t="n">
-        <v>4.041</v>
+        <v>0.3039</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0339</v>
+        <v>-0.8294</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0547</v>
+        <v>2.4405</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2192</v>
+        <v>3.9645</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1645</v>
+        <v>-1.524</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3238</v>
+        <v>2.3655</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2376</v>
+        <v>2.395</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0862</v>
+        <v>-0.0295</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7377</v>
+        <v>3.3857</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1009</v>
+        <v>2.7311</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6368</v>
+        <v>0.6546</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4138</v>
+        <v>-1.0202</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1367</v>
+        <v>-0.3362</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5506</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5527</v>
+        <v>0.2392</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3039</v>
+        <v>0.6833</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8566</v>
+        <v>-0.4441</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4477</v>
+        <v>0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1179</v>
+        <v>1.8358</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6863</v>
+        <v>2.2087</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2648</v>
+        <v>1.8762</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5785</v>
+        <v>0.3325</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3655</v>
+        <v>2.7521</v>
       </c>
       <c r="H8" t="n">
-        <v>2.395</v>
+        <v>2.6998</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0295</v>
+        <v>0.0523</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3857</v>
+        <v>2.2755</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7311</v>
+        <v>2.2121</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6546</v>
+        <v>0.0634</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0202</v>
+        <v>0.4766</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3362</v>
+        <v>0.4877</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.485</v>
+        <v>-0.2613</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9836</v>
+        <v>0.5709</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4986</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.4456</v>
+        <v>1.9093</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2766</v>
+        <v>-1.1186</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1689</v>
+        <v>3.0278</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7521</v>
+        <v>1.0972</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6998</v>
+        <v>-0.3131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0523</v>
+        <v>1.4103</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2755</v>
+        <v>-0.6475</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2121</v>
+        <v>-1.5406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0634</v>
+        <v>0.8931</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4766</v>
+        <v>1.7447</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4877</v>
+        <v>1.2275</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0111</v>
+        <v>0.5172</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0244</v>
+        <v>2.3643</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9713000000000001</v>
+        <v>2.4394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9957</v>
+        <v>-0.0751</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2154</v>
+        <v>0.7159</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2793</v>
+        <v>1.7798</v>
       </c>
       <c r="F10" t="n">
         <v>-1.0639</v>
@@ -1234,10 +1234,10 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8255</v>
+        <v>-0.325</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2905</v>
+        <v>0.21</v>
       </c>
       <c r="U10" t="n">
         <v>-0.535</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4226</v>
+        <v>-0.2224</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1953</v>
+        <v>0.3955</v>
       </c>
       <c r="F11" t="n">
         <v>-0.6179</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.461</v>
+        <v>-0.2608</v>
       </c>
       <c r="T11" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2731</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2629</v>
+        <v>-1.1356</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1547</v>
+        <v>0.2548</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4176</v>
+        <v>-1.3904</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3417</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3093</v>
+        <v>-0.182</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.173</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2449</v>
+        <v>-2.4535</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.223</v>
+        <v>-2.0228</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.022</v>
+        <v>-0.4308</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2434</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5507</v>
+        <v>0.3421</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3768</v>
+        <v>0.577</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1739</v>
+        <v>-0.2349</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>44.54349999999999</v>
+        <v>44.5435</v>
       </c>
       <c r="E14" t="n">
-        <v>35.3965</v>
+        <v>35.39660000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>9.146599999999998</v>
+        <v>9.146699999999999</v>
       </c>
       <c r="G14" t="n">
         <v>34.51899999999999</v>
@@ -1534,7 +1534,7 @@
         <v>3.1221</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.8341999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-1.9403</v>
@@ -1546,13 +1546,13 @@
         <v>12.6121</v>
       </c>
       <c r="S14" t="n">
-        <v>8.058599999999998</v>
+        <v>8.058700000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>11.4118</v>
+        <v>11.4119</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.3531</v>
+        <v>-3.3533</v>
       </c>
       <c r="V14" t="n">
         <v>3.905899999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1415</v>
+        <v>-1.6138</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0006</v>
+        <v>3.1007</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1421</v>
+        <v>-4.7144</v>
       </c>
       <c r="G16" t="n">
         <v>-2.874</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1019</v>
+        <v>0.4259</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6449</v>
+        <v>0.745</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7467</v>
+        <v>-0.3191</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3299</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7909</v>
+        <v>-1.9295</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0049</v>
+        <v>-1.3042</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.786</v>
+        <v>-0.6253</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2918</v>
@@ -1780,13 +1780,13 @@
         <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1707</v>
+        <v>-0.3093</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.157</v>
+        <v>0.5437</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0137</v>
+        <v>-0.8529</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>B. BAILLO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6296</v>
+        <v>-3.0895</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2511</v>
+        <v>0.244</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8806</v>
+        <v>-3.3335</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.2671</v>
+        <v>-2.6643</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.1704</v>
+        <v>-2.166</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0966</v>
+        <v>-0.4983</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0737</v>
+        <v>0.4877</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.969</v>
+        <v>-0.243</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8953</v>
+        <v>0.7307</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.1934</v>
+        <v>-3.152</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2014</v>
+        <v>-1.9229</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.992</v>
+        <v>-1.229</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7539</v>
+        <v>-1.5492</v>
       </c>
       <c r="T18" t="n">
-        <v>3.0114</v>
+        <v>-0.2437</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.2575</v>
+        <v>-1.3055</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2716</v>
+        <v>-0.2343</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0478</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BAILLO HERNÁNDEZ</t>
+          <t>D. CARABALLO ROPERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7</v>
+        <v>-3.8478</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4567</v>
+        <v>-1.6619</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2434</v>
+        <v>-2.1859</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6643</v>
+        <v>-1.8181</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.166</v>
+        <v>-1.5456</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4983</v>
+        <v>-0.2725</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4877</v>
+        <v>-0.6261</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.243</v>
+        <v>-0.6261</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7307</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.152</v>
+        <v>-1.192</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9229</v>
+        <v>-0.9195</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.229</v>
+        <v>-0.2725</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1597</v>
+        <v>-0.4178</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9444</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2153</v>
+        <v>-0.3522</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2343</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2343</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>J. ALIK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7524</v>
+        <v>-4.0726</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4428</v>
+        <v>-0.2445</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.1952</v>
+        <v>-3.8281</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.6045</v>
+        <v>-3.0533</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.1976</v>
+        <v>-2.1602</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4069</v>
+        <v>-0.8931</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4167</v>
+        <v>-0.5215</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.1297</v>
+        <v>-1.2523</v>
       </c>
       <c r="L20" t="n">
-        <v>0.713</v>
+        <v>0.7307</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.1878</v>
+        <v>-2.5318</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0679</v>
+        <v>-0.9079</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.1198</v>
+        <v>-1.6239</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5224</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2999</v>
+        <v>-0.0477</v>
       </c>
       <c r="T20" t="n">
-        <v>2.8297</v>
+        <v>-0.0051</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5298</v>
+        <v>-0.0426</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ALIK</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0604</v>
+        <v>-4.5338</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0443</v>
+        <v>-0.3505</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0161</v>
+        <v>-4.1833</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0533</v>
+        <v>-5.2671</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1602</v>
+        <v>-4.1704</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8931</v>
+        <v>-1.0966</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5215</v>
+        <v>-0.0737</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2523</v>
+        <v>-1.969</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7307</v>
+        <v>1.8953</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5318</v>
+        <v>-5.1934</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9079</v>
+        <v>-2.2014</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6239</v>
+        <v>-2.992</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>2.5224</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0355</v>
+        <v>-0.1503</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1951</v>
+        <v>1.4098</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2306</v>
+        <v>-1.5601</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5537</v>
+        <v>1.2716</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CARABALLO ROPERO</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5574</v>
+        <v>-4.7534</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2625</v>
+        <v>-0.9586</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2949</v>
+        <v>-3.7948</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8181</v>
+        <v>-6.6045</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5456</v>
+        <v>-4.1976</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2725</v>
+        <v>-2.4069</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6261</v>
+        <v>-1.4167</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6261</v>
+        <v>-2.1297</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.192</v>
+        <v>-5.1878</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9195</v>
+        <v>-2.0679</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2725</v>
+        <v>-3.1198</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5821</v>
+        <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1274</v>
+        <v>0.2989</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6662</v>
+        <v>1.4283</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4612</v>
+        <v>-1.1294</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.3644</v>
+        <v>-7.479</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9136</v>
+        <v>-4.5132</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4508</v>
+        <v>-2.9658</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5634</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.607</v>
+        <v>-1.7216</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4834</v>
+        <v>-0.083</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.1236</v>
+        <v>-1.6386</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.5707</v>
+        <v>-9.5786</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.201</v>
+        <v>-3.5003</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.3697</v>
+        <v>-6.0783</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4673</v>
@@ -2326,13 +2326,13 @@
         <v>2.7164</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.8497</v>
+        <v>-1.8576</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0162</v>
+        <v>-0.3155</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.8335</v>
+        <v>-1.5421</v>
       </c>
       <c r="V24" t="n">
         <v>-3.0597</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-44.54340000000001</v>
+        <v>-41.8741</v>
       </c>
       <c r="E25" t="n">
         <v>-9.146699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-35.3967</v>
+        <v>-32.7273</v>
       </c>
       <c r="G25" t="n">
         <v>-34.5193</v>
@@ -2383,7 +2383,7 @@
         <v>-3.1222</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8343999999999987</v>
+        <v>0.8343999999999996</v>
       </c>
       <c r="M25" t="n">
         <v>-32.2315</v>
@@ -2404,13 +2404,13 @@
         <v>14.5523</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.0587</v>
+        <v>-5.3893</v>
       </c>
       <c r="T25" t="n">
         <v>3.3533</v>
       </c>
       <c r="U25" t="n">
-        <v>-11.4119</v>
+        <v>-8.7425</v>
       </c>
       <c r="V25" t="n">
         <v>-3.906</v>
